--- a/reports/Debug-snowbowl-20251230/For Winter Ending (Actual)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20251230/For Winter Ending (Actual)_Revenue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>DepartmentTitle</t>
   </si>
@@ -55,22 +55,19 @@
     <t>account</t>
   </si>
   <si>
+    <t xml:space="preserve">T101                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T104                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T100                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T257                     </t>
+  </si>
+  <si>
     <t xml:space="preserve">T103                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T100                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T257                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T101                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T104                     </t>
   </si>
   <si>
     <t>department</t>
@@ -488,24 +485,22 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2">
-        <v>284415.5300</v>
+        <v>-4667.4200</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -513,13 +508,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2">
-        <v>3772631.7900</v>
+        <v>233.7500</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -527,13 +522,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2">
-        <v>348.0400</v>
+        <v>-17.9500</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -541,13 +536,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2">
-        <v>-4667.4200</v>
+        <v>3772631.7900</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -555,13 +550,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2">
-        <v>233.7500</v>
+        <v>348.0400</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -569,13 +564,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="2">
-        <v>-17.9500</v>
+        <v>284415.5300</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -584,7 +579,7 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2">
         <v>410070.7000</v>
@@ -596,7 +591,7 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2">
         <v>1163398.4500</v>
@@ -608,7 +603,7 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" s="2">
         <v>19055.4200</v>
@@ -620,7 +615,7 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="2">
         <v>499205.7200</v>
@@ -632,7 +627,7 @@
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2">
         <v>2488.9200</v>
@@ -644,7 +639,7 @@
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2">
         <v>456007.3600</v>
@@ -656,7 +651,7 @@
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2">
         <v>711822.0000</v>
@@ -668,7 +663,7 @@
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" s="2">
         <v>52307.0300</v>
@@ -680,7 +675,7 @@
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="2">
         <v>60473.8000</v>
@@ -692,7 +687,7 @@
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" s="2">
         <v>0.0700</v>
